--- a/resurse/oferte/cereri/cerere-oferta-pepiniera-mizil.xlsx
+++ b/resurse/oferte/cereri/cerere-oferta-pepiniera-mizil.xlsx
@@ -491,14 +491,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>De la: ______________________ · telefon: ______________ · e-mail: ______________</t>
+          <t>De la: George Șerban · telefon: 0765468714 · e-mail: george357ro@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data cererii: ____ . ____ . 2026</t>
+          <t>Data cererii: 6 octombrie 2026</t>
         </is>
       </c>
     </row>

--- a/resurse/oferte/cereri/cerere-oferta-pepiniera-mizil.xlsx
+++ b/resurse/oferte/cereri/cerere-oferta-pepiniera-mizil.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -571,16 +571,16 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Sorb</t>
+          <t>Corn</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Sorbus torminalis</t>
+          <t>Cornus mas</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -600,16 +600,16 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Păr sălbatic</t>
+          <t>Alun</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Pyrus pyraster</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -629,16 +629,16 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Cireș sălbatic</t>
+          <t>Salbă moale</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Prunus avium</t>
+          <t>Euonymus europaeus</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Corn</t>
+          <t>Călin</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Cornus mas</t>
+          <t>Viburnum opulus</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -682,266 +682,34 @@
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Alun</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>1–2 ani, 30–80 cm, rădăcină nudă sau ghiveci 1–2 l</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5">
-        <f>D15*F15</f>
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7">
+        <f>SUM(D11:D14)</f>
         <v/>
       </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Porumbar</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Prunus spinosa</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>1–2 ani, 30–80 cm, rădăcină nudă sau ghiveci 1–2 l</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5">
-        <f>D16*F16</f>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7">
+        <f>SUM(G11:G14)</f>
         <v/>
       </c>
-      <c r="H16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Dârmox</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Viburnum lantana</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>1–2 ani, 30–80 cm, rădăcină nudă sau ghiveci 1–2 l</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5">
-        <f>D17*F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="H15" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Vă rugăm să precizați: costul transportului la Crucea sau adresa de ridicare, termenul de valabilitate al ofertei, dacă puteți rezerva cantitățile până la confirmare, și eventualele specii pe care nu le aveți (cu propuneri de înlocuire).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Salbă moale</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Euonymus europaeus</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>1–2 ani, 30–80 cm, rădăcină nudă sau ghiveci 1–2 l</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5">
-        <f>D18*F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Călin</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Viburnum opulus</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>1–2 ani, 30–80 cm, rădăcină nudă sau ghiveci 1–2 l</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5">
-        <f>D19*F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Soc</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Sambucus nigra</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>1–2 ani, 30–80 cm, rădăcină nudă sau ghiveci 1–2 l</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5">
-        <f>D20*F20</f>
-        <v/>
-      </c>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Arbore de mazăre</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Caragana arborescens</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>1–2 ani, 30–80 cm, rădăcină nudă sau ghiveci 1–2 l</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5">
-        <f>D21*F21</f>
-        <v/>
-      </c>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Pin negru</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Pinus nigra</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>ghiveci 2–3 l sau balot, 30–60 cm</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5">
-        <f>D22*F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr"/>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr"/>
-      <c r="D23" s="7">
-        <f>SUM(D11:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7">
-        <f>SUM(G11:G22)</f>
-        <v/>
-      </c>
-      <c r="H23" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Vă rugăm să precizați: costul transportului la Crucea sau adresa de ridicare, termenul de valabilitate al ofertei, dacă puteți rezerva cantitățile până la confirmare, și eventualele specii pe care nu le aveți (cu propuneri de înlocuire).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Vă mulțumim.</t>
         </is>
@@ -950,9 +718,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/resurse/oferte/cereri/cerere-oferta-pepiniera-mizil.xlsx
+++ b/resurse/oferte/cereri/cerere-oferta-pepiniera-mizil.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>

--- a/resurse/oferte/cereri/cerere-oferta-pepiniera-mizil.xlsx
+++ b/resurse/oferte/cereri/cerere-oferta-pepiniera-mizil.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
